--- a/Hardware/CNC_controller/Project Outputs for CNC_controller/CNC_controller.xlsx
+++ b/Hardware/CNC_controller/Project Outputs for CNC_controller/CNC_controller.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan Manuel Mejia V\Desktop\Proyectos\CNC_Multi\Hardware\CNC_controller\Project Outputs for CNC_controller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A912A924-800C-4424-BE99-1423B4E02BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1165265-BAA1-41DE-BE03-86B0668B27E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2DAF7ECE-3E88-4375-B764-70EAC61CF6A6}"/>
+    <workbookView xWindow="2540" yWindow="2540" windowWidth="14400" windowHeight="7270" xr2:uid="{2DAF7ECE-3E88-4375-B764-70EAC61CF6A6}"/>
   </bookViews>
   <sheets>
     <sheet name="CNC_controller" sheetId="1" r:id="rId1"/>
